--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
@@ -565,67 +565,67 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3526</v>
+        <v>5.385899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2013</v>
+        <v>2.6447</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1514</v>
+        <v>2.7412</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8386</v>
+        <v>5.8551</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1171999999999997</v>
+        <v>0.1185999999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>5.721500000000001</v>
+        <v>5.7366</v>
       </c>
       <c r="J2" t="n">
-        <v>7.668200000000001</v>
+        <v>7.9255</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2429000000000003</v>
+        <v>-0.08699999999999974</v>
       </c>
       <c r="L2" t="n">
-        <v>7.9111</v>
+        <v>8.0124</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8297</v>
+        <v>-2.0702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3599999999999999</v>
+        <v>0.2056000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1896</v>
+        <v>-2.2759</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q2" t="n">
-        <v>-8.6036</v>
+        <v>-8.503</v>
       </c>
       <c r="R2" t="n">
-        <v>6.555099999999999</v>
+        <v>6.478499999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3085000000000001</v>
+        <v>-0.3104</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1851999999999999</v>
+        <v>0.2465999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4937</v>
+        <v>-0.5569999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8711</v>
+        <v>1.8657</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9515</v>
+        <v>2.9755</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0804</v>
+        <v>-1.1098</v>
       </c>
     </row>
     <row r="3">
@@ -643,31 +643,31 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8345</v>
+        <v>3.8669</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8345</v>
+        <v>3.8669</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8345</v>
+        <v>3.8669</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4636</v>
+        <v>1.4816</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3709</v>
+        <v>2.3852</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8345</v>
+        <v>3.8669</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4636</v>
+        <v>1.4816</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3709</v>
+        <v>2.3852</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8447</v>
+        <v>0.8435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9941</v>
+        <v>1.0057</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1495</v>
+        <v>-0.1621</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1758</v>
+        <v>1.1716</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="I4" t="n">
-        <v>1.148</v>
+        <v>1.1514</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2645</v>
+        <v>1.2722</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2645</v>
+        <v>1.2722</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0887</v>
+        <v>-0.1006</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1164</v>
+        <v>-0.1207</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1263</v>
+        <v>-0.1256</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0655</v>
+        <v>-0.064</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0608</v>
+        <v>-0.0616</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2060999999999997</v>
+        <v>-0.2176999999999998</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9146999999999998</v>
+        <v>-0.5258000000000003</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.3081</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2632</v>
+        <v>-2.3315</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2818</v>
+        <v>-1.2659</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9812000000000001</v>
+        <v>-1.0655</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8012</v>
+        <v>1.9749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6158999999999999</v>
+        <v>0.7822</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1855</v>
+        <v>1.1927</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.0644</v>
+        <v>-4.3062</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8977</v>
+        <v>-2.0481</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.166700000000001</v>
+        <v>-2.2582</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.4823</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.8085</v>
+        <v>-8.705400000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>5.326</v>
+        <v>5.2638</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1713</v>
+        <v>1.1516</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5376999999999998</v>
+        <v>0.5978000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6335000000000002</v>
+        <v>0.5537</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3682</v>
+        <v>4.4037</v>
       </c>
       <c r="W5" t="n">
-        <v>5.5548</v>
+        <v>5.6068</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1865</v>
+        <v>-1.2031</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8789999999999997</v>
+        <v>-1.0066</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1868</v>
+        <v>-1.7582</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3077</v>
+        <v>0.7514999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.217700000000001</v>
+        <v>-4.3094</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7925999999999999</v>
+        <v>0.6779000000000002</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.010300000000001</v>
+        <v>-4.987299999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4514</v>
+        <v>2.68</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6667</v>
+        <v>3.7515</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2152</v>
+        <v>-1.0716</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.6692</v>
+        <v>-6.9895</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.8741</v>
+        <v>-3.0734</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.7951</v>
+        <v>-3.916</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8437</v>
+        <v>1.822</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.7357</v>
+        <v>-5.668699999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5793</v>
+        <v>7.4908</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07840000000000003</v>
+        <v>0.05259999999999998</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7478</v>
+        <v>-1.6517</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8261</v>
+        <v>1.7044</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4168</v>
+        <v>1.4282</v>
       </c>
       <c r="W6" t="n">
-        <v>2.845400000000001</v>
+        <v>2.8822</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4286</v>
+        <v>-1.454</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4885</v>
+        <v>-1.499099999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8037</v>
+        <v>-0.5380999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6848000000000001</v>
+        <v>-0.9608000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.7376</v>
+        <v>-3.7347</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0238</v>
+        <v>-2.0354</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7139</v>
+        <v>-1.6994</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8417000000000001</v>
+        <v>-0.6811999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8272</v>
+        <v>-1.7437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.0626</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8958</v>
+        <v>-3.0536</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1965000000000001</v>
+        <v>-0.2916000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.6992</v>
+        <v>-2.762</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8678</v>
+        <v>2.8344</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8921</v>
+        <v>3.8466</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1583</v>
+        <v>-0.1483</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4962</v>
+        <v>-0.4436</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3378</v>
+        <v>0.2953</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4603999999999999</v>
+        <v>-0.4503</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5586</v>
+        <v>1.5988</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.019</v>
+        <v>-2.0491</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.32</v>
+        <v>-4.3434</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.8094</v>
+        <v>-4.6883</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4892999999999998</v>
+        <v>0.345</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9445</v>
+        <v>-2.9708</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8885000000000001</v>
+        <v>0.8519000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.833</v>
+        <v>-3.8226</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1892</v>
+        <v>-1.1308</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5267999999999999</v>
+        <v>0.5335</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7161</v>
+        <v>-1.6642</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7553</v>
+        <v>-1.8399</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3618</v>
+        <v>0.3185</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.117</v>
+        <v>-2.1583</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4097000000000001</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2532</v>
+        <v>-2.2271</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0719</v>
+        <v>-1.0611</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6703</v>
+        <v>-0.6423</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4016999999999999</v>
+        <v>-0.4188</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000006</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8027</v>
+        <v>0.7815000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.505000000000001</v>
+        <v>-4.5563</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4434</v>
+        <v>-0.1305000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0617</v>
+        <v>-4.4256</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4462</v>
+        <v>0.6412</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1245</v>
+        <v>-2.7868</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5707</v>
+        <v>3.4279</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1782</v>
+        <v>4.9143</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6049</v>
+        <v>-0.2213000000000003</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5733</v>
+        <v>5.1356</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.6244</v>
+        <v>-4.2732</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4804</v>
+        <v>-2.5655</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.144</v>
+        <v>-1.7078</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2046999999999998</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.7357</v>
+        <v>-6.0737</v>
       </c>
       <c r="R9" t="n">
-        <v>5.9405</v>
+        <v>2.6319</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.37</v>
+        <v>-2.0999</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.0347</v>
+        <v>-1.6027</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3352</v>
+        <v>-0.4971</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1062</v>
+        <v>0.3440999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1489</v>
+        <v>2.6313</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0427</v>
+        <v>-2.2872</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6095</v>
+        <v>-4.559</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4052</v>
+        <v>-2.0002</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2044</v>
+        <v>-2.5586</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6548</v>
+        <v>-1.5164</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7791</v>
+        <v>1.0326</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4337</v>
+        <v>-2.5491</v>
       </c>
       <c r="J10" t="n">
-        <v>4.79</v>
+        <v>3.4135</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2970999999999999</v>
+        <v>2.7031</v>
       </c>
       <c r="L10" t="n">
-        <v>5.087</v>
+        <v>0.7103000000000002</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.1352</v>
+        <v>-4.9298</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.482</v>
+        <v>-1.6705</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6532</v>
+        <v>-3.2593</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4823</v>
+        <v>0.2025999999999998</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.145300000000001</v>
+        <v>-5.668699999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>2.663</v>
+        <v>5.8712</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.13</v>
+        <v>-3.3382</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.6529</v>
+        <v>-1.9389</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4772999999999999</v>
+        <v>-1.3994</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3483000000000002</v>
+        <v>0.09320000000000006</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6033</v>
+        <v>2.1939</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.255</v>
+        <v>-2.1006</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.241899999999999</v>
+        <v>-8.2311</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.4336</v>
+        <v>-4.401</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1917</v>
+        <v>-3.830099999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.042200000000001</v>
+        <v>1.685</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3014</v>
+        <v>0.2952000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3436</v>
+        <v>1.3901</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7507</v>
+        <v>5.8482</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>2.4239</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7507999999999999</v>
+        <v>3.4245</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.7929</v>
+        <v>-4.1632</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6984999999999999</v>
+        <v>-2.1287</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.0944</v>
+        <v>-2.0344</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.326</v>
+        <v>-3.8466</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.423</v>
+        <v>-7.8957</v>
       </c>
       <c r="R11" t="n">
-        <v>4.0969</v>
+        <v>4.0491</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5474</v>
+        <v>-3.5831</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8887999999999997</v>
+        <v>-3.1066</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6585</v>
+        <v>-0.4766</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.420999999999999</v>
+        <v>-2.4865</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.6501</v>
+        <v>0.7528</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7709</v>
+        <v>-3.2393</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.3283</v>
+        <v>-8.257299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8287</v>
+        <v>-8.132</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4996</v>
+        <v>-0.1253000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6532</v>
+        <v>-1.1185</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2680000000000005</v>
+        <v>1.2857</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3851</v>
+        <v>-2.4042</v>
       </c>
       <c r="J12" t="n">
-        <v>5.6186</v>
+        <v>2.846</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2768</v>
+        <v>2.0907</v>
       </c>
       <c r="L12" t="n">
-        <v>3.3417</v>
+        <v>0.7553</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.9655</v>
+        <v>-3.9645</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0088</v>
+        <v>-0.805</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9566</v>
+        <v>-3.1594</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.8921</v>
+        <v>-5.2638</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.989</v>
+        <v>-9.312799999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>4.0969</v>
+        <v>4.0491</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.6159</v>
+        <v>2.5057</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.1843</v>
+        <v>0.9302999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4315</v>
+        <v>1.5755</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4733</v>
+        <v>-4.3809</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7262</v>
+        <v>-2.5956</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.1995</v>
+        <v>-1.7853</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.7028</v>
+        <v>-8.653600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0027</v>
+        <v>-4.5831</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7001</v>
+        <v>-4.0704</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7629</v>
+        <v>-2.7104</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7464</v>
+        <v>2.804</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.509399999999999</v>
+        <v>-5.5144</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0059</v>
+        <v>2.2607</v>
       </c>
       <c r="K13" t="n">
-        <v>4.839</v>
+        <v>5.0309</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8331</v>
+        <v>-2.7702</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.769</v>
+        <v>-4.971</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0926</v>
+        <v>-2.2268</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6763</v>
+        <v>-2.7442</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4823</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.6036</v>
+        <v>-8.503</v>
       </c>
       <c r="R13" t="n">
-        <v>5.1212</v>
+        <v>5.0613</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0229</v>
+        <v>2.0083</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8072</v>
+        <v>1.8456</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2157</v>
+        <v>0.1628</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.480399999999999</v>
+        <v>-4.5098</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2123</v>
+        <v>-0.1865</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.268000000000001</v>
+        <v>-4.323399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.2493</v>
+        <v>-31.2278</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.7983</v>
+        <v>-19.2399</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.451499999999999</v>
+        <v>-11.9871</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.257400000000001</v>
+        <v>-5.471899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6453</v>
+        <v>2.479600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.902899999999998</v>
+        <v>-7.951299999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>33.3323</v>
+        <v>35.1902</v>
       </c>
       <c r="K14" t="n">
-        <v>15.6265</v>
+        <v>16.7454</v>
       </c>
       <c r="L14" t="n">
-        <v>17.7058</v>
+        <v>18.4448</v>
       </c>
       <c r="M14" t="n">
-        <v>-38.5901</v>
+        <v>-40.6617</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.981</v>
+        <v>-14.2653</v>
       </c>
       <c r="O14" t="n">
-        <v>-25.6085</v>
+        <v>-26.3962</v>
       </c>
       <c r="P14" t="n">
-        <v>-17.4118</v>
+        <v>-17.2087</v>
       </c>
       <c r="Q14" t="n">
-        <v>-64.5266</v>
+        <v>-63.77289999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>47.1146</v>
+        <v>46.56440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.960900000000001</v>
+        <v>-4.948399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.4328</v>
+        <v>-5.829499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4714</v>
+        <v>0.8811999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.618299999999999</v>
+        <v>-3.599400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>14.8298</v>
+        <v>15.1709</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.4479</v>
+        <v>-18.7703</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. STARLABS MORÓN.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.385899999999999</v>
+        <v>5.519</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6447</v>
+        <v>2.1896</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7412</v>
+        <v>3.329499999999999</v>
       </c>
       <c r="G2" t="n">
         <v>5.8551</v>
@@ -610,13 +610,13 @@
         <v>6.478499999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3104</v>
+        <v>-0.1771999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2465999999999999</v>
+        <v>-0.2085000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5569999999999999</v>
+        <v>0.03110000000000002</v>
       </c>
       <c r="V2" t="n">
         <v>1.8657</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8435</v>
+        <v>0.9588</v>
       </c>
       <c r="E4" t="n">
         <v>1.0057</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1621</v>
+        <v>-0.0469</v>
       </c>
       <c r="G4" t="n">
         <v>1.1716</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1256</v>
+        <v>-0.0104</v>
       </c>
       <c r="T4" t="n">
         <v>-0.064</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0616</v>
+        <v>0.0537</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2176999999999998</v>
+        <v>-0.3997000000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5258000000000003</v>
+        <v>-0.7597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3081</v>
+        <v>0.3599000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3315</v>
+        <v>-4.3094</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2659</v>
+        <v>0.6779000000000002</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0655</v>
+        <v>-4.987299999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9749</v>
+        <v>2.68</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7822</v>
+        <v>3.7515</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1927</v>
+        <v>-1.0716</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.3062</v>
+        <v>-6.9895</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0481</v>
+        <v>-3.0734</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2582</v>
+        <v>-3.916</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.4418</v>
+        <v>1.822</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.705400000000001</v>
+        <v>-5.668699999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>5.2638</v>
+        <v>7.4908</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1516</v>
+        <v>0.6594</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5978000000000001</v>
+        <v>-0.6533</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5537</v>
+        <v>1.3128</v>
       </c>
       <c r="V5" t="n">
-        <v>4.4037</v>
+        <v>1.4282</v>
       </c>
       <c r="W5" t="n">
-        <v>5.6068</v>
+        <v>2.8822</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2031</v>
+        <v>-1.454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0066</v>
+        <v>-0.7200999999999995</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7582</v>
+        <v>-0.5779000000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7514999999999998</v>
+        <v>-0.1421999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.3094</v>
+        <v>-3.7347</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6779000000000002</v>
+        <v>-2.0354</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.987299999999999</v>
+        <v>-1.6994</v>
       </c>
       <c r="J6" t="n">
-        <v>2.68</v>
+        <v>-0.6811999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7515</v>
+        <v>-1.7437</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0716</v>
+        <v>1.0626</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.9895</v>
+        <v>-3.0536</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.0734</v>
+        <v>-0.2916000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.916</v>
+        <v>-2.762</v>
       </c>
       <c r="P6" t="n">
-        <v>1.822</v>
+        <v>2.8344</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.668699999999999</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>7.4908</v>
+        <v>3.8466</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05259999999999998</v>
+        <v>0.6307</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6517</v>
+        <v>-0.4834000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7044</v>
+        <v>1.114</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4282</v>
+        <v>-0.4503</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8822</v>
+        <v>1.5988</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.454</v>
+        <v>-2.0491</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.499099999999999</v>
+        <v>-1.3419</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5380999999999999</v>
+        <v>-1.356400000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9608000000000001</v>
+        <v>0.01429999999999987</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.7347</v>
+        <v>-2.3315</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0354</v>
+        <v>-1.2659</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6994</v>
+        <v>-1.0655</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6811999999999999</v>
+        <v>1.9749</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7437</v>
+        <v>0.7822</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0626</v>
+        <v>1.1927</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0536</v>
+        <v>-4.3062</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2916000000000001</v>
+        <v>-2.0481</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.762</v>
+        <v>-2.2582</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8344</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0123</v>
+        <v>-8.705400000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8466</v>
+        <v>5.2638</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1483</v>
+        <v>0.02729999999999988</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4436</v>
+        <v>-0.2326999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2953</v>
+        <v>0.26</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4503</v>
+        <v>4.4037</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5988</v>
+        <v>5.6068</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0491</v>
+        <v>-1.2031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3434</v>
+        <v>-3.3281</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.6883</v>
+        <v>0.3885999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.345</v>
+        <v>-3.7166</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9708</v>
+        <v>0.6412</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8519000000000001</v>
+        <v>-2.7868</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8226</v>
+        <v>3.4279</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1308</v>
+        <v>4.9143</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5335</v>
+        <v>-0.2213000000000003</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6642</v>
+        <v>5.1356</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8399</v>
+        <v>-4.2732</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3185</v>
+        <v>-2.5655</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1583</v>
+        <v>-1.7078</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4049</v>
+        <v>-3.4418</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2271</v>
+        <v>-6.0737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8221</v>
+        <v>2.6319</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0611</v>
+        <v>-0.8716999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6423</v>
+        <v>-1.0837</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4188</v>
+        <v>0.2119</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09320000000000006</v>
+        <v>0.3440999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6883</v>
+        <v>2.6313</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7815000000000001</v>
+        <v>-2.2872</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5563</v>
+        <v>-3.4808</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1305000000000001</v>
+        <v>-1.6887</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.4256</v>
+        <v>-1.7921</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6412</v>
+        <v>-1.5164</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7868</v>
+        <v>1.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4279</v>
+        <v>-2.5491</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9143</v>
+        <v>3.4135</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2213000000000003</v>
+        <v>2.7031</v>
       </c>
       <c r="L9" t="n">
-        <v>5.1356</v>
+        <v>0.7103000000000002</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.2732</v>
+        <v>-4.9298</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5655</v>
+        <v>-1.6705</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7078</v>
+        <v>-3.2593</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.4418</v>
+        <v>0.2025999999999998</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0737</v>
+        <v>-5.668699999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6319</v>
+        <v>5.8712</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0999</v>
+        <v>-2.2601</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.6027</v>
+        <v>-1.6275</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4971</v>
+        <v>-0.6327</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3440999999999999</v>
+        <v>0.09320000000000006</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6313</v>
+        <v>2.1939</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2872</v>
+        <v>-2.1006</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.559</v>
+        <v>-3.6977</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0002</v>
+        <v>-4.273099999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5586</v>
+        <v>0.5754999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5164</v>
+        <v>-2.9708</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0326</v>
+        <v>0.8519000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5491</v>
+        <v>-3.8226</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4135</v>
+        <v>-1.1308</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7031</v>
+        <v>0.5335</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7103000000000002</v>
+        <v>-1.6642</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.9298</v>
+        <v>-1.8399</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6705</v>
+        <v>0.3185</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2593</v>
+        <v>-2.1583</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2025999999999998</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.668699999999999</v>
+        <v>-2.2271</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8712</v>
+        <v>1.8221</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.3382</v>
+        <v>-0.4152</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9389</v>
+        <v>-0.227</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3994</v>
+        <v>-0.1884</v>
       </c>
       <c r="V10" t="n">
         <v>0.09320000000000006</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1939</v>
+        <v>-0.6883</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1006</v>
+        <v>0.7815000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.2311</v>
+        <v>-5.572</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.401</v>
+        <v>-2.3645</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.830099999999999</v>
+        <v>-3.2075</v>
       </c>
       <c r="G11" t="n">
         <v>1.685</v>
@@ -1312,13 +1312,13 @@
         <v>4.0491</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.5831</v>
+        <v>-0.924</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.1066</v>
+        <v>-1.07</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4766</v>
+        <v>0.1461</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4865</v>
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.257299999999999</v>
+        <v>-9.7845</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.132</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1253000000000001</v>
+        <v>-0.5745000000000005</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1185</v>
@@ -1390,13 +1390,13 @@
         <v>4.0491</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5057</v>
+        <v>0.9785999999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9302999999999999</v>
+        <v>-0.1477</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5755</v>
+        <v>1.1262</v>
       </c>
       <c r="V12" t="n">
         <v>-4.3809</v>
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.653600000000001</v>
+        <v>-10.1589</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5831</v>
+        <v>-6.1403</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0704</v>
+        <v>-4.0184</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7104</v>
@@ -1468,13 +1468,13 @@
         <v>5.0613</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0083</v>
+        <v>0.5030999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8456</v>
+        <v>0.2883</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1628</v>
+        <v>0.2146999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-4.5098</v>
@@ -1501,22 +1501,22 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.2278</v>
+        <v>-28.139</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.2399</v>
+        <v>-18.9198</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.9871</v>
+        <v>-9.219000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.471899999999999</v>
+        <v>-5.4719</v>
       </c>
       <c r="H14" t="n">
         <v>2.479600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.951299999999998</v>
+        <v>-7.9513</v>
       </c>
       <c r="J14" t="n">
         <v>35.1902</v>
@@ -1546,13 +1546,13 @@
         <v>46.56440000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.948399999999999</v>
+        <v>-1.859500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.829499999999999</v>
+        <v>-5.509500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8811999999999999</v>
+        <v>3.6494</v>
       </c>
       <c r="V14" t="n">
         <v>-3.599400000000001</v>
